--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="47">
   <si>
     <t>No.</t>
   </si>
@@ -35,25 +35,43 @@
     <t>평균</t>
   </si>
   <si>
+    <t>486.6</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
     <t>447.1</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>4.5</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>526.1</t>
+  </si>
+  <si>
+    <t>973.2</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>03일</t>
   </si>
   <si>
     <t>04일</t>
@@ -445,16 +463,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s" s="31">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s" s="32">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -462,19 +480,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -482,19 +500,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -502,19 +520,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -522,19 +540,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -542,19 +560,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -562,19 +580,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -582,19 +600,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -602,19 +620,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -622,19 +640,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -642,19 +660,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -662,19 +680,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -682,19 +700,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -702,19 +720,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -722,19 +740,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -742,19 +760,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -762,19 +780,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -782,19 +800,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -802,19 +820,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -822,19 +840,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -842,19 +860,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -862,19 +880,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -882,19 +900,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -902,19 +920,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -922,19 +940,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -942,19 +960,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -962,19 +980,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -982,19 +1000,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1002,19 +1020,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1022,19 +1040,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="51">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>486.6</t>
+    <t>479.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.9</t>
+    <t>4.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -71,10 +71,22 @@
     <t>03일</t>
   </si>
   <si>
+    <t>463.7</t>
+  </si>
+  <si>
+    <t>1436.9</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>14.4</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>04일</t>
   </si>
   <si>
     <t>05일</t>
@@ -506,13 +518,13 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -520,19 +532,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -540,19 +552,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -560,19 +572,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -580,19 +592,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -600,19 +612,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -620,19 +632,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -640,19 +652,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -660,19 +672,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -680,19 +692,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -700,19 +712,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -720,19 +732,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -740,19 +752,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -760,19 +772,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -780,19 +792,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -800,19 +812,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -820,19 +832,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -840,19 +852,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -860,19 +872,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -880,19 +892,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -900,19 +912,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -920,19 +932,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -940,19 +952,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -960,19 +972,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -980,19 +992,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1000,19 +1012,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1020,19 +1032,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1040,19 +1052,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="54">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>479.0</t>
+    <t>446.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.8</t>
+    <t>4.5</t>
   </si>
   <si>
     <t>01일</t>
@@ -50,9 +50,6 @@
     <t>447.1</t>
   </si>
   <si>
-    <t>4.5</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
@@ -86,10 +83,22 @@
     <t>04일</t>
   </si>
   <si>
+    <t>349.1</t>
+  </si>
+  <si>
+    <t>1786.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>17.9</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>05일</t>
   </si>
   <si>
     <t>06일</t>
@@ -481,10 +490,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -492,19 +501,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s" s="36">
         <v>13</v>
       </c>
-      <c r="C4" t="s" s="36">
+      <c r="D4" t="s" s="37">
         <v>14</v>
       </c>
-      <c r="D4" t="s" s="37">
+      <c r="E4" t="s" s="38">
         <v>15</v>
       </c>
-      <c r="E4" t="s" s="38">
+      <c r="F4" t="s" s="39">
         <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -512,19 +521,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s" s="31">
         <v>18</v>
       </c>
-      <c r="C5" t="s" s="31">
+      <c r="D5" t="s" s="32">
         <v>19</v>
       </c>
-      <c r="D5" t="s" s="32">
+      <c r="E5" t="s" s="33">
         <v>20</v>
       </c>
-      <c r="E5" t="s" s="33">
+      <c r="F5" t="s" s="34">
         <v>21</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -532,19 +541,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>23</v>
-      </c>
-      <c r="C6" t="s" s="36">
-        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
         <v>24</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -552,19 +561,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -572,19 +581,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -592,19 +601,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -612,19 +621,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -632,19 +641,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -652,19 +661,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -672,19 +681,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -692,19 +701,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -712,19 +721,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -732,19 +741,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -752,19 +761,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -772,19 +781,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -792,19 +801,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -812,19 +821,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -832,19 +841,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -852,19 +861,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -872,19 +881,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -892,19 +901,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -912,19 +921,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -932,19 +941,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -952,19 +961,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -972,19 +981,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -992,19 +1001,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1012,19 +1021,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1032,19 +1041,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1052,19 +1061,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="63">
   <si>
     <t>No.</t>
   </si>
@@ -35,21 +35,24 @@
     <t>평균</t>
   </si>
   <si>
-    <t>446.5</t>
+    <t>472.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>447.1</t>
+  </si>
+  <si>
     <t>4.5</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>447.1</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
@@ -98,13 +101,37 @@
     <t>05일</t>
   </si>
   <si>
+    <t>497.0</t>
+  </si>
+  <si>
+    <t>2283.0</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>22.8</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>552.4</t>
+  </si>
+  <si>
+    <t>2835.4</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.4</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>07일</t>
   </si>
   <si>
     <t>08일</t>
@@ -490,10 +517,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -501,19 +528,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -521,19 +548,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -541,19 +568,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -561,19 +588,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -581,19 +608,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -601,19 +628,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -621,19 +648,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -641,19 +668,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -661,19 +688,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -681,19 +708,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -701,19 +728,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -721,19 +748,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -741,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -761,19 +788,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -781,19 +808,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -801,19 +828,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -821,19 +848,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -841,19 +868,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -861,19 +888,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -881,19 +908,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -901,19 +928,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -921,19 +948,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -941,19 +968,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -961,19 +988,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -981,19 +1008,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1001,19 +1028,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1021,19 +1048,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1041,19 +1068,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1061,19 +1088,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="81">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>472.6</t>
+    <t>445.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
+    <t>4.4</t>
   </si>
   <si>
     <t>01일</t>
@@ -116,10 +116,10 @@
     <t>06일</t>
   </si>
   <si>
-    <t>552.4</t>
-  </si>
-  <si>
-    <t>2835.4</t>
+    <t>552.6</t>
+  </si>
+  <si>
+    <t>2835.6</t>
   </si>
   <si>
     <t>5.5</t>
@@ -131,22 +131,76 @@
     <t>07일</t>
   </si>
   <si>
+    <t>267.5</t>
+  </si>
+  <si>
+    <t>3103.1</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>31.0</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>393.1</t>
+  </si>
+  <si>
+    <t>3496.2</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>35.0</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>478.4</t>
+  </si>
+  <si>
+    <t>3974.6</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>39.7</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>463.0</t>
+  </si>
+  <si>
+    <t>4437.6</t>
+  </si>
+  <si>
+    <t>44.4</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>457.3</t>
+  </si>
+  <si>
+    <t>4894.9</t>
+  </si>
+  <si>
+    <t>48.9</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>12일</t>
   </si>
   <si>
     <t>13일</t>
@@ -634,13 +688,13 @@
         <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -648,19 +702,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -668,19 +722,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -688,19 +742,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -708,19 +762,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>39</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -728,19 +782,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -748,19 +802,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -768,19 +822,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -788,19 +842,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -808,19 +862,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -828,19 +882,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -848,19 +902,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -868,19 +922,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -888,19 +942,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -908,19 +962,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -928,19 +982,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -948,19 +1002,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -968,19 +1022,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -988,19 +1042,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1008,19 +1062,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1028,19 +1082,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1048,19 +1102,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1068,19 +1122,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1088,19 +1142,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>445.0</t>
+    <t>447.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.4</t>
+    <t>4.5</t>
   </si>
   <si>
     <t>01일</t>
@@ -50,9 +50,6 @@
     <t>447.1</t>
   </si>
   <si>
-    <t>4.5</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
@@ -188,13 +185,16 @@
     <t>11일</t>
   </si>
   <si>
-    <t>457.3</t>
-  </si>
-  <si>
-    <t>4894.9</t>
-  </si>
-  <si>
-    <t>48.9</t>
+    <t>486.0</t>
+  </si>
+  <si>
+    <t>4923.6</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>49.2</t>
   </si>
   <si>
     <t>12일</t>
@@ -571,10 +571,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -582,19 +582,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s" s="36">
         <v>13</v>
       </c>
-      <c r="C4" t="s" s="36">
+      <c r="D4" t="s" s="37">
         <v>14</v>
       </c>
-      <c r="D4" t="s" s="37">
+      <c r="E4" t="s" s="38">
         <v>15</v>
       </c>
-      <c r="E4" t="s" s="38">
+      <c r="F4" t="s" s="39">
         <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -602,19 +602,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s" s="31">
         <v>18</v>
       </c>
-      <c r="C5" t="s" s="31">
+      <c r="D5" t="s" s="32">
         <v>19</v>
       </c>
-      <c r="D5" t="s" s="32">
+      <c r="E5" t="s" s="33">
         <v>20</v>
       </c>
-      <c r="E5" t="s" s="33">
+      <c r="F5" t="s" s="34">
         <v>21</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -622,19 +622,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>23</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>24</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>25</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>26</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -642,19 +642,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>28</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>29</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>30</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>31</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -662,19 +662,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>33</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>34</v>
       </c>
-      <c r="D8" t="s" s="37">
+      <c r="E8" t="s" s="38">
         <v>35</v>
       </c>
-      <c r="E8" t="s" s="38">
+      <c r="F8" t="s" s="39">
         <v>36</v>
-      </c>
-      <c r="F8" t="s" s="39">
-        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -682,19 +682,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>38</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>39</v>
       </c>
-      <c r="D9" t="s" s="32">
+      <c r="E9" t="s" s="33">
         <v>40</v>
       </c>
-      <c r="E9" t="s" s="33">
+      <c r="F9" t="s" s="34">
         <v>41</v>
-      </c>
-      <c r="F9" t="s" s="34">
-        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -702,19 +702,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>43</v>
       </c>
-      <c r="C10" t="s" s="36">
+      <c r="D10" t="s" s="37">
         <v>44</v>
       </c>
-      <c r="D10" t="s" s="37">
+      <c r="E10" t="s" s="38">
         <v>45</v>
       </c>
-      <c r="E10" t="s" s="38">
+      <c r="F10" t="s" s="39">
         <v>46</v>
-      </c>
-      <c r="F10" t="s" s="39">
-        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -722,19 +722,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s" s="31">
         <v>48</v>
       </c>
-      <c r="C11" t="s" s="31">
+      <c r="D11" t="s" s="32">
         <v>49</v>
       </c>
-      <c r="D11" t="s" s="32">
+      <c r="E11" t="s" s="33">
         <v>50</v>
       </c>
-      <c r="E11" t="s" s="33">
+      <c r="F11" t="s" s="34">
         <v>51</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -742,19 +742,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>53</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>54</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
+        <v>20</v>
+      </c>
+      <c r="F12" t="s" s="39">
         <v>55</v>
-      </c>
-      <c r="E12" t="s" s="38">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -762,16 +762,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>57</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>58</v>
       </c>
-      <c r="D13" t="s" s="32">
+      <c r="E13" t="s" s="33">
         <v>59</v>
-      </c>
-      <c r="E13" t="s" s="33">
-        <v>21</v>
       </c>
       <c r="F13" t="s" s="34">
         <v>60</v>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="85">
   <si>
     <t>No.</t>
   </si>
@@ -35,21 +35,24 @@
     <t>평균</t>
   </si>
   <si>
-    <t>447.6</t>
+    <t>457.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>447.1</t>
+  </si>
+  <si>
     <t>4.5</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>447.1</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
@@ -74,9 +77,6 @@
     <t>1436.9</t>
   </si>
   <si>
-    <t>4.6</t>
-  </si>
-  <si>
     <t>14.4</t>
   </si>
   <si>
@@ -200,10 +200,22 @@
     <t>12일</t>
   </si>
   <si>
+    <t>565.2</t>
+  </si>
+  <si>
+    <t>5488.8</t>
+  </si>
+  <si>
+    <t>5.7</t>
+  </si>
+  <si>
+    <t>54.9</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>13일</t>
   </si>
   <si>
     <t>14일</t>
@@ -571,10 +583,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -582,19 +594,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -602,16 +614,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s" s="34">
         <v>21</v>
@@ -751,7 +763,7 @@
         <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s" s="39">
         <v>55</v>
@@ -788,13 +800,13 @@
         <v>62</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -802,19 +814,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -822,19 +834,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -842,19 +854,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -862,19 +874,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -882,19 +894,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -902,19 +914,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -922,19 +934,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -942,19 +954,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -962,19 +974,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -982,19 +994,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1002,19 +1014,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1022,19 +1034,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1042,19 +1054,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1062,19 +1074,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1082,19 +1094,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1102,19 +1114,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1122,19 +1134,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1142,19 +1154,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="90">
   <si>
     <t>No.</t>
   </si>
@@ -35,48 +35,51 @@
     <t>평균</t>
   </si>
   <si>
-    <t>457.4</t>
+    <t>467.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>447.1</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>526.1</t>
+  </si>
+  <si>
+    <t>973.2</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>463.7</t>
+  </si>
+  <si>
+    <t>1436.9</t>
+  </si>
+  <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>447.1</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>526.1</t>
-  </si>
-  <si>
-    <t>973.2</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>463.7</t>
-  </si>
-  <si>
-    <t>1436.9</t>
-  </si>
-  <si>
     <t>14.4</t>
   </si>
   <si>
@@ -215,10 +218,22 @@
     <t>13일</t>
   </si>
   <si>
+    <t>582.9</t>
+  </si>
+  <si>
+    <t>6071.7</t>
+  </si>
+  <si>
+    <t>5.8</t>
+  </si>
+  <si>
+    <t>60.7</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>14일</t>
   </si>
   <si>
     <t>15일</t>
@@ -623,10 +638,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -634,19 +649,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -654,19 +669,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -674,19 +689,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -694,19 +709,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -714,19 +729,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -734,19 +749,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -754,19 +769,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -774,19 +789,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -794,19 +809,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -814,19 +829,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -834,19 +849,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -854,19 +869,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -874,19 +889,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -894,19 +909,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -914,19 +929,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -934,19 +949,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -954,19 +969,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -974,19 +989,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -994,19 +1009,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1014,19 +1029,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1034,19 +1049,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1054,19 +1069,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1074,19 +1089,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1094,19 +1109,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1114,19 +1129,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1134,19 +1149,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1154,19 +1169,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="93">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>467.1</t>
+    <t>468.1</t>
   </si>
   <si>
     <t>-</t>
@@ -233,10 +233,19 @@
     <t>14일</t>
   </si>
   <si>
+    <t>481.7</t>
+  </si>
+  <si>
+    <t>6553.4</t>
+  </si>
+  <si>
+    <t>65.5</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>15일</t>
   </si>
   <si>
     <t>16일</t>
@@ -855,13 +864,13 @@
         <v>73</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -869,19 +878,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -889,19 +898,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -909,19 +918,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -929,19 +938,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -949,19 +958,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -969,19 +978,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -989,19 +998,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1009,19 +1018,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1029,19 +1038,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1049,19 +1058,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1069,19 +1078,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1089,19 +1098,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1109,19 +1118,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1129,19 +1138,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1149,19 +1158,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1169,19 +1178,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="95">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>468.1</t>
+    <t>475.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
+    <t>4.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -167,9 +167,6 @@
     <t>3974.6</t>
   </si>
   <si>
-    <t>4.8</t>
-  </si>
-  <si>
     <t>39.7</t>
   </si>
   <si>
@@ -245,10 +242,19 @@
     <t>15일</t>
   </si>
   <si>
+    <t>580.4</t>
+  </si>
+  <si>
+    <t>7133.8</t>
+  </si>
+  <si>
+    <t>71.3</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>16일</t>
   </si>
   <si>
     <t>17일</t>
@@ -767,10 +773,10 @@
         <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s" s="34">
         <v>51</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -778,19 +784,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>53</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>54</v>
-      </c>
-      <c r="D12" t="s" s="37">
-        <v>55</v>
       </c>
       <c r="E12" t="s" s="38">
         <v>21</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -798,19 +804,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>57</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>58</v>
       </c>
-      <c r="D13" t="s" s="32">
+      <c r="E13" t="s" s="33">
         <v>59</v>
       </c>
-      <c r="E13" t="s" s="33">
+      <c r="F13" t="s" s="34">
         <v>60</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -818,19 +824,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>62</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>63</v>
       </c>
-      <c r="D14" t="s" s="37">
+      <c r="E14" t="s" s="38">
         <v>64</v>
       </c>
-      <c r="E14" t="s" s="38">
+      <c r="F14" t="s" s="39">
         <v>65</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -838,19 +844,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>67</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>68</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>69</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>70</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -858,19 +864,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>72</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>73</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s" s="39">
         <v>74</v>
-      </c>
-      <c r="E16" t="s" s="38">
-        <v>51</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -878,19 +884,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>76</v>
-      </c>
-      <c r="C17" t="s" s="31">
-        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
         <v>77</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -898,19 +904,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -918,19 +924,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -938,19 +944,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -958,19 +964,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -978,19 +984,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -998,19 +1004,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1018,19 +1024,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1038,19 +1044,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1058,19 +1064,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1078,19 +1084,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1098,19 +1104,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1118,19 +1124,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1138,19 +1144,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1158,19 +1164,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1178,19 +1184,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="98">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>475.6</t>
+    <t>481.9</t>
   </si>
   <si>
     <t>-</t>
@@ -254,10 +254,19 @@
     <t>16일</t>
   </si>
   <si>
+    <t>576.2</t>
+  </si>
+  <si>
+    <t>7710.0</t>
+  </si>
+  <si>
+    <t>77.1</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>17일</t>
   </si>
   <si>
     <t>18일</t>
@@ -910,13 +919,13 @@
         <v>80</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -924,19 +933,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -944,19 +953,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -964,19 +973,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -984,19 +993,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1004,19 +1013,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1024,19 +1033,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1044,19 +1053,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1064,19 +1073,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1084,19 +1093,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1104,19 +1113,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1124,19 +1133,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1144,19 +1153,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1164,19 +1173,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1184,19 +1193,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="102">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>481.9</t>
+    <t>483.4</t>
   </si>
   <si>
     <t>-</t>
@@ -266,10 +266,22 @@
     <t>17일</t>
   </si>
   <si>
+    <t>508.6</t>
+  </si>
+  <si>
+    <t>8218.6</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>82.2</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>18일</t>
   </si>
   <si>
     <t>19일</t>
@@ -939,13 +951,13 @@
         <v>84</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -953,19 +965,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -973,19 +985,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -993,19 +1005,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1013,19 +1025,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1033,19 +1045,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1053,19 +1065,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1073,19 +1085,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1093,19 +1105,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1113,19 +1125,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1133,19 +1145,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1153,19 +1165,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1173,19 +1185,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1193,19 +1205,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="105">
   <si>
     <t>No.</t>
   </si>
@@ -35,138 +35,141 @@
     <t>평균</t>
   </si>
   <si>
-    <t>483.4</t>
+    <t>488.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>447.1</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>526.1</t>
+  </si>
+  <si>
+    <t>973.2</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>463.7</t>
+  </si>
+  <si>
+    <t>1436.9</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>14.4</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>349.1</t>
+  </si>
+  <si>
+    <t>1786.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>17.9</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>497.0</t>
+  </si>
+  <si>
+    <t>2283.0</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>22.8</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>552.6</t>
+  </si>
+  <si>
+    <t>2835.6</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.4</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>267.5</t>
+  </si>
+  <si>
+    <t>3103.1</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>31.0</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>393.1</t>
+  </si>
+  <si>
+    <t>3496.2</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>35.0</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>478.4</t>
+  </si>
+  <si>
+    <t>3974.6</t>
+  </si>
+  <si>
     <t>4.8</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>447.1</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>526.1</t>
-  </si>
-  <si>
-    <t>973.2</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>463.7</t>
-  </si>
-  <si>
-    <t>1436.9</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>14.4</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>349.1</t>
-  </si>
-  <si>
-    <t>1786.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>17.9</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>497.0</t>
-  </si>
-  <si>
-    <t>2283.0</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>22.8</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>552.6</t>
-  </si>
-  <si>
-    <t>2835.6</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>28.4</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>267.5</t>
-  </si>
-  <si>
-    <t>3103.1</t>
-  </si>
-  <si>
-    <t>2.7</t>
-  </si>
-  <si>
-    <t>31.0</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>393.1</t>
-  </si>
-  <si>
-    <t>3496.2</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>35.0</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>478.4</t>
-  </si>
-  <si>
-    <t>3974.6</t>
-  </si>
-  <si>
     <t>39.7</t>
   </si>
   <si>
@@ -191,9 +194,6 @@
     <t>4923.6</t>
   </si>
   <si>
-    <t>4.9</t>
-  </si>
-  <si>
     <t>49.2</t>
   </si>
   <si>
@@ -281,10 +281,19 @@
     <t>18일</t>
   </si>
   <si>
+    <t>566.7</t>
+  </si>
+  <si>
+    <t>8785.3</t>
+  </si>
+  <si>
+    <t>87.9</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>19일</t>
   </si>
   <si>
     <t>20일</t>
@@ -794,10 +803,10 @@
         <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -805,19 +814,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s" s="38">
         <v>21</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -825,16 +834,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s" s="34">
         <v>60</v>
@@ -894,7 +903,7 @@
         <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s" s="39">
         <v>74</v>
@@ -971,13 +980,13 @@
         <v>89</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -985,19 +994,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1005,19 +1014,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1025,19 +1034,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1045,19 +1054,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1065,19 +1074,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1085,19 +1094,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1105,19 +1114,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1125,19 +1134,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1145,19 +1154,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1165,19 +1174,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1185,19 +1194,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1205,19 +1214,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="109">
   <si>
     <t>No.</t>
   </si>
@@ -35,165 +35,165 @@
     <t>평균</t>
   </si>
   <si>
-    <t>488.1</t>
+    <t>484.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>447.1</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>526.1</t>
+  </si>
+  <si>
+    <t>973.2</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>463.7</t>
+  </si>
+  <si>
+    <t>1436.9</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>14.4</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>349.1</t>
+  </si>
+  <si>
+    <t>1786.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>17.9</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>497.0</t>
+  </si>
+  <si>
+    <t>2283.0</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>22.8</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>552.6</t>
+  </si>
+  <si>
+    <t>2835.6</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.4</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>267.5</t>
+  </si>
+  <si>
+    <t>3103.1</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>31.0</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>393.1</t>
+  </si>
+  <si>
+    <t>3496.2</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>35.0</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>478.4</t>
+  </si>
+  <si>
+    <t>3974.6</t>
+  </si>
+  <si>
+    <t>39.7</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>463.0</t>
+  </si>
+  <si>
+    <t>4437.6</t>
+  </si>
+  <si>
+    <t>44.4</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>486.0</t>
+  </si>
+  <si>
+    <t>4923.6</t>
+  </si>
+  <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>447.1</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>526.1</t>
-  </si>
-  <si>
-    <t>973.2</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>463.7</t>
-  </si>
-  <si>
-    <t>1436.9</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>14.4</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>349.1</t>
-  </si>
-  <si>
-    <t>1786.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>17.9</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>497.0</t>
-  </si>
-  <si>
-    <t>2283.0</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>22.8</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>552.6</t>
-  </si>
-  <si>
-    <t>2835.6</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>28.4</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>267.5</t>
-  </si>
-  <si>
-    <t>3103.1</t>
-  </si>
-  <si>
-    <t>2.7</t>
-  </si>
-  <si>
-    <t>31.0</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>393.1</t>
-  </si>
-  <si>
-    <t>3496.2</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>35.0</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>478.4</t>
-  </si>
-  <si>
-    <t>3974.6</t>
-  </si>
-  <si>
-    <t>4.8</t>
-  </si>
-  <si>
-    <t>39.7</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>463.0</t>
-  </si>
-  <si>
-    <t>4437.6</t>
-  </si>
-  <si>
-    <t>44.4</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>486.0</t>
-  </si>
-  <si>
-    <t>4923.6</t>
-  </si>
-  <si>
     <t>49.2</t>
   </si>
   <si>
@@ -293,10 +293,22 @@
     <t>19일</t>
   </si>
   <si>
+    <t>411.4</t>
+  </si>
+  <si>
+    <t>9196.7</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>92.0</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>20일</t>
   </si>
   <si>
     <t>21일</t>
@@ -803,10 +815,10 @@
         <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s" s="34">
         <v>51</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -814,19 +826,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>53</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>54</v>
-      </c>
-      <c r="D12" t="s" s="37">
-        <v>55</v>
       </c>
       <c r="E12" t="s" s="38">
         <v>21</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -834,16 +846,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>57</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>58</v>
       </c>
-      <c r="D13" t="s" s="32">
+      <c r="E13" t="s" s="33">
         <v>59</v>
-      </c>
-      <c r="E13" t="s" s="33">
-        <v>9</v>
       </c>
       <c r="F13" t="s" s="34">
         <v>60</v>
@@ -903,7 +915,7 @@
         <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s" s="39">
         <v>74</v>
@@ -1000,13 +1012,13 @@
         <v>93</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1014,19 +1026,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1034,19 +1046,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1054,19 +1066,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1074,19 +1086,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1094,19 +1106,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1114,19 +1126,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1134,19 +1146,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1154,19 +1166,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1174,19 +1186,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1194,19 +1206,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1214,19 +1226,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="114">
   <si>
     <t>No.</t>
   </si>
@@ -35,138 +35,141 @@
     <t>평균</t>
   </si>
   <si>
-    <t>484.0</t>
+    <t>465.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>447.1</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>526.1</t>
+  </si>
+  <si>
+    <t>973.2</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>463.7</t>
+  </si>
+  <si>
+    <t>1436.9</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>14.4</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>349.1</t>
+  </si>
+  <si>
+    <t>1786.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>17.9</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>497.0</t>
+  </si>
+  <si>
+    <t>2283.0</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>22.8</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>552.6</t>
+  </si>
+  <si>
+    <t>2835.6</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.4</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>267.5</t>
+  </si>
+  <si>
+    <t>3103.1</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>31.0</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>393.1</t>
+  </si>
+  <si>
+    <t>3496.2</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>35.0</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>478.4</t>
+  </si>
+  <si>
+    <t>3974.6</t>
+  </si>
+  <si>
     <t>4.8</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>447.1</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>526.1</t>
-  </si>
-  <si>
-    <t>973.2</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>463.7</t>
-  </si>
-  <si>
-    <t>1436.9</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>14.4</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>349.1</t>
-  </si>
-  <si>
-    <t>1786.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>17.9</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>497.0</t>
-  </si>
-  <si>
-    <t>2283.0</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>22.8</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>552.6</t>
-  </si>
-  <si>
-    <t>2835.6</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>28.4</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>267.5</t>
-  </si>
-  <si>
-    <t>3103.1</t>
-  </si>
-  <si>
-    <t>2.7</t>
-  </si>
-  <si>
-    <t>31.0</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>393.1</t>
-  </si>
-  <si>
-    <t>3496.2</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>35.0</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>478.4</t>
-  </si>
-  <si>
-    <t>3974.6</t>
-  </si>
-  <si>
     <t>39.7</t>
   </si>
   <si>
@@ -308,10 +311,22 @@
     <t>20일</t>
   </si>
   <si>
+    <t>114.4</t>
+  </si>
+  <si>
+    <t>9311.1</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>93.1</t>
+  </si>
+  <si>
+    <t>21일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>21일</t>
   </si>
   <si>
     <t>22일</t>
@@ -815,10 +830,10 @@
         <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -826,19 +841,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s" s="38">
         <v>21</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -846,19 +861,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -866,19 +881,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -886,19 +901,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -906,19 +921,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -926,19 +941,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -946,19 +961,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -966,19 +981,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -986,19 +1001,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1006,19 +1021,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1026,19 +1041,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1046,19 +1061,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1066,19 +1081,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1086,19 +1101,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1106,19 +1121,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1126,19 +1141,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1146,19 +1161,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1166,19 +1181,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1186,19 +1201,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1206,19 +1221,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1226,19 +1241,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="117">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>465.6</t>
+    <t>461.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
+    <t>4.6</t>
   </si>
   <si>
     <t>01일</t>
@@ -77,9 +77,6 @@
     <t>1436.9</t>
   </si>
   <si>
-    <t>4.6</t>
-  </si>
-  <si>
     <t>14.4</t>
   </si>
   <si>
@@ -326,10 +323,22 @@
     <t>21일</t>
   </si>
   <si>
+    <t>372.0</t>
+  </si>
+  <si>
+    <t>9683.1</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>96.8</t>
+  </si>
+  <si>
+    <t>22일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>22일</t>
   </si>
   <si>
     <t>23일</t>
@@ -710,10 +719,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s" s="34">
         <v>21</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -721,19 +730,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>23</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>24</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>25</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>26</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -741,19 +750,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>28</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>29</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>30</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>31</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -761,19 +770,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>33</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>34</v>
       </c>
-      <c r="D8" t="s" s="37">
+      <c r="E8" t="s" s="38">
         <v>35</v>
       </c>
-      <c r="E8" t="s" s="38">
+      <c r="F8" t="s" s="39">
         <v>36</v>
-      </c>
-      <c r="F8" t="s" s="39">
-        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -781,19 +790,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>38</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>39</v>
       </c>
-      <c r="D9" t="s" s="32">
+      <c r="E9" t="s" s="33">
         <v>40</v>
       </c>
-      <c r="E9" t="s" s="33">
+      <c r="F9" t="s" s="34">
         <v>41</v>
-      </c>
-      <c r="F9" t="s" s="34">
-        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -801,19 +810,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>43</v>
       </c>
-      <c r="C10" t="s" s="36">
+      <c r="D10" t="s" s="37">
         <v>44</v>
       </c>
-      <c r="D10" t="s" s="37">
+      <c r="E10" t="s" s="38">
         <v>45</v>
       </c>
-      <c r="E10" t="s" s="38">
+      <c r="F10" t="s" s="39">
         <v>46</v>
-      </c>
-      <c r="F10" t="s" s="39">
-        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -821,19 +830,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s" s="31">
         <v>48</v>
       </c>
-      <c r="C11" t="s" s="31">
+      <c r="D11" t="s" s="32">
         <v>49</v>
       </c>
-      <c r="D11" t="s" s="32">
+      <c r="E11" t="s" s="33">
         <v>50</v>
       </c>
-      <c r="E11" t="s" s="33">
+      <c r="F11" t="s" s="34">
         <v>51</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -841,19 +850,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>53</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>54</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s" s="39">
         <v>55</v>
-      </c>
-      <c r="E12" t="s" s="38">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -861,19 +870,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>57</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>58</v>
       </c>
-      <c r="D13" t="s" s="32">
+      <c r="E13" t="s" s="33">
         <v>59</v>
       </c>
-      <c r="E13" t="s" s="33">
+      <c r="F13" t="s" s="34">
         <v>60</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -881,19 +890,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>62</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>63</v>
       </c>
-      <c r="D14" t="s" s="37">
+      <c r="E14" t="s" s="38">
         <v>64</v>
       </c>
-      <c r="E14" t="s" s="38">
+      <c r="F14" t="s" s="39">
         <v>65</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -901,19 +910,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>67</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>68</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>69</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>70</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -921,19 +930,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>72</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>73</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
+        <v>50</v>
+      </c>
+      <c r="F16" t="s" s="39">
         <v>74</v>
-      </c>
-      <c r="E16" t="s" s="38">
-        <v>51</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -941,19 +950,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>76</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>77</v>
       </c>
-      <c r="D17" t="s" s="32">
+      <c r="E17" t="s" s="33">
+        <v>69</v>
+      </c>
+      <c r="F17" t="s" s="34">
         <v>78</v>
-      </c>
-      <c r="E17" t="s" s="33">
-        <v>70</v>
-      </c>
-      <c r="F17" t="s" s="34">
-        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -961,19 +970,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>80</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>81</v>
       </c>
-      <c r="D18" t="s" s="37">
+      <c r="E18" t="s" s="38">
+        <v>69</v>
+      </c>
+      <c r="F18" t="s" s="39">
         <v>82</v>
-      </c>
-      <c r="E18" t="s" s="38">
-        <v>70</v>
-      </c>
-      <c r="F18" t="s" s="39">
-        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -981,19 +990,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>84</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>85</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
         <v>86</v>
       </c>
-      <c r="E19" t="s" s="33">
+      <c r="F19" t="s" s="34">
         <v>87</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>88</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1001,19 +1010,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>89</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>90</v>
       </c>
-      <c r="D20" t="s" s="37">
+      <c r="E20" t="s" s="38">
+        <v>64</v>
+      </c>
+      <c r="F20" t="s" s="39">
         <v>91</v>
-      </c>
-      <c r="E20" t="s" s="38">
-        <v>65</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1021,19 +1030,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>93</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>94</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
         <v>95</v>
       </c>
-      <c r="E21" t="s" s="33">
+      <c r="F21" t="s" s="34">
         <v>96</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1041,19 +1050,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>97</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>98</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>99</v>
       </c>
-      <c r="D22" t="s" s="37">
+      <c r="E22" t="s" s="38">
         <v>100</v>
       </c>
-      <c r="E22" t="s" s="38">
+      <c r="F22" t="s" s="39">
         <v>101</v>
-      </c>
-      <c r="F22" t="s" s="39">
-        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1061,19 +1070,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
+        <v>102</v>
+      </c>
+      <c r="C23" t="s" s="31">
         <v>103</v>
-      </c>
-      <c r="C23" t="s" s="31">
-        <v>104</v>
       </c>
       <c r="D23" t="s" s="32">
         <v>104</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1081,19 +1090,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1101,19 +1110,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1121,19 +1130,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1141,19 +1150,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1161,19 +1170,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1181,19 +1190,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1201,19 +1210,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1221,19 +1230,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1241,19 +1250,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="124">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>461.1</t>
+    <t>463.7</t>
   </si>
   <si>
     <t>-</t>
@@ -71,9 +71,6 @@
     <t>03일</t>
   </si>
   <si>
-    <t>463.7</t>
-  </si>
-  <si>
     <t>1436.9</t>
   </si>
   <si>
@@ -338,13 +335,37 @@
     <t>22일</t>
   </si>
   <si>
+    <t>376.1</t>
+  </si>
+  <si>
+    <t>10059.2</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>100.6</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
+    <t>606.4</t>
+  </si>
+  <si>
+    <t>10665.6</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>106.7</t>
+  </si>
+  <si>
+    <t>24일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>23일</t>
-  </si>
-  <si>
-    <t>24일</t>
   </si>
   <si>
     <t>25일</t>
@@ -713,16 +734,16 @@
         <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s" s="32">
         <v>19</v>
-      </c>
-      <c r="D5" t="s" s="32">
-        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
         <v>9</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -730,19 +751,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>22</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>23</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>24</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>25</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -750,19 +771,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>27</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>28</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>29</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>30</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -770,19 +791,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>32</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>33</v>
       </c>
-      <c r="D8" t="s" s="37">
+      <c r="E8" t="s" s="38">
         <v>34</v>
       </c>
-      <c r="E8" t="s" s="38">
+      <c r="F8" t="s" s="39">
         <v>35</v>
-      </c>
-      <c r="F8" t="s" s="39">
-        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -790,19 +811,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>37</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>38</v>
       </c>
-      <c r="D9" t="s" s="32">
+      <c r="E9" t="s" s="33">
         <v>39</v>
       </c>
-      <c r="E9" t="s" s="33">
+      <c r="F9" t="s" s="34">
         <v>40</v>
-      </c>
-      <c r="F9" t="s" s="34">
-        <v>41</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -810,19 +831,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>42</v>
       </c>
-      <c r="C10" t="s" s="36">
+      <c r="D10" t="s" s="37">
         <v>43</v>
       </c>
-      <c r="D10" t="s" s="37">
+      <c r="E10" t="s" s="38">
         <v>44</v>
       </c>
-      <c r="E10" t="s" s="38">
+      <c r="F10" t="s" s="39">
         <v>45</v>
-      </c>
-      <c r="F10" t="s" s="39">
-        <v>46</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -830,19 +851,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s" s="31">
         <v>47</v>
       </c>
-      <c r="C11" t="s" s="31">
+      <c r="D11" t="s" s="32">
         <v>48</v>
       </c>
-      <c r="D11" t="s" s="32">
+      <c r="E11" t="s" s="33">
         <v>49</v>
       </c>
-      <c r="E11" t="s" s="33">
+      <c r="F11" t="s" s="34">
         <v>50</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -850,19 +871,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>52</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>53</v>
-      </c>
-      <c r="D12" t="s" s="37">
-        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
         <v>9</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -870,19 +891,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>55</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>56</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>57</v>
       </c>
-      <c r="D13" t="s" s="32">
+      <c r="E13" t="s" s="33">
         <v>58</v>
       </c>
-      <c r="E13" t="s" s="33">
+      <c r="F13" t="s" s="34">
         <v>59</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>60</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -890,19 +911,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>61</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>62</v>
       </c>
-      <c r="D14" t="s" s="37">
+      <c r="E14" t="s" s="38">
         <v>63</v>
       </c>
-      <c r="E14" t="s" s="38">
+      <c r="F14" t="s" s="39">
         <v>64</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>65</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -910,19 +931,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>66</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>67</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>68</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>69</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>70</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -930,19 +951,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>71</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>72</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
+        <v>49</v>
+      </c>
+      <c r="F16" t="s" s="39">
         <v>73</v>
-      </c>
-      <c r="E16" t="s" s="38">
-        <v>50</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>74</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -950,19 +971,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>75</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>76</v>
       </c>
-      <c r="D17" t="s" s="32">
+      <c r="E17" t="s" s="33">
+        <v>68</v>
+      </c>
+      <c r="F17" t="s" s="34">
         <v>77</v>
-      </c>
-      <c r="E17" t="s" s="33">
-        <v>69</v>
-      </c>
-      <c r="F17" t="s" s="34">
-        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -970,19 +991,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>79</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>80</v>
       </c>
-      <c r="D18" t="s" s="37">
+      <c r="E18" t="s" s="38">
+        <v>68</v>
+      </c>
+      <c r="F18" t="s" s="39">
         <v>81</v>
-      </c>
-      <c r="E18" t="s" s="38">
-        <v>69</v>
-      </c>
-      <c r="F18" t="s" s="39">
-        <v>82</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -990,19 +1011,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>83</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>84</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
         <v>85</v>
       </c>
-      <c r="E19" t="s" s="33">
+      <c r="F19" t="s" s="34">
         <v>86</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1010,19 +1031,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>88</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>89</v>
       </c>
-      <c r="D20" t="s" s="37">
+      <c r="E20" t="s" s="38">
+        <v>63</v>
+      </c>
+      <c r="F20" t="s" s="39">
         <v>90</v>
-      </c>
-      <c r="E20" t="s" s="38">
-        <v>64</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>91</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1030,19 +1051,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>91</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>92</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>93</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
         <v>94</v>
       </c>
-      <c r="E21" t="s" s="33">
+      <c r="F21" t="s" s="34">
         <v>95</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>96</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1050,19 +1071,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>96</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>97</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>98</v>
       </c>
-      <c r="D22" t="s" s="37">
+      <c r="E22" t="s" s="38">
         <v>99</v>
       </c>
-      <c r="E22" t="s" s="38">
+      <c r="F22" t="s" s="39">
         <v>100</v>
-      </c>
-      <c r="F22" t="s" s="39">
-        <v>101</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1070,19 +1091,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
+        <v>101</v>
+      </c>
+      <c r="C23" t="s" s="31">
         <v>102</v>
       </c>
-      <c r="C23" t="s" s="31">
+      <c r="D23" t="s" s="32">
         <v>103</v>
       </c>
-      <c r="D23" t="s" s="32">
+      <c r="E23" t="s" s="33">
         <v>104</v>
       </c>
-      <c r="E23" t="s" s="33">
+      <c r="F23" t="s" s="34">
         <v>105</v>
-      </c>
-      <c r="F23" t="s" s="34">
-        <v>106</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1090,19 +1111,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="C24" t="s" s="36">
         <v>107</v>
-      </c>
-      <c r="C24" t="s" s="36">
-        <v>108</v>
       </c>
       <c r="D24" t="s" s="37">
         <v>108</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1110,19 +1131,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1130,19 +1151,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1150,19 +1171,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1170,19 +1191,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1190,19 +1211,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1210,19 +1231,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1230,19 +1251,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1250,19 +1271,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="128">
   <si>
     <t>No.</t>
   </si>
@@ -35,45 +35,51 @@
     <t>평균</t>
   </si>
   <si>
+    <t>465.1</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>447.1</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>526.1</t>
+  </si>
+  <si>
+    <t>973.2</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
     <t>463.7</t>
   </si>
   <si>
-    <t>-</t>
+    <t>1436.9</t>
   </si>
   <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>447.1</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>526.1</t>
-  </si>
-  <si>
-    <t>973.2</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>1436.9</t>
-  </si>
-  <si>
     <t>14.4</t>
   </si>
   <si>
@@ -365,10 +371,16 @@
     <t>24일</t>
   </si>
   <si>
+    <t>11162.6</t>
+  </si>
+  <si>
+    <t>111.6</t>
+  </si>
+  <si>
+    <t>25일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>25일</t>
   </si>
   <si>
     <t>26일</t>
@@ -734,16 +746,16 @@
         <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -751,19 +763,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -771,19 +783,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -791,19 +803,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -811,19 +823,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -831,19 +843,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -851,19 +863,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -871,19 +883,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -891,19 +903,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -911,19 +923,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -931,19 +943,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -951,19 +963,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -971,19 +983,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -991,19 +1003,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1011,19 +1023,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1031,19 +1043,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1051,19 +1063,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1071,19 +1083,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1091,19 +1103,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1111,19 +1123,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1131,19 +1143,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1151,19 +1163,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1171,19 +1183,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1191,19 +1203,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1211,19 +1223,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1231,19 +1243,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1251,19 +1263,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1271,19 +1283,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="131">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>465.1</t>
+    <t>458.2</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
+    <t>4.6</t>
   </si>
   <si>
     <t>01일</t>
@@ -77,9 +77,6 @@
     <t>1436.9</t>
   </si>
   <si>
-    <t>4.6</t>
-  </si>
-  <si>
     <t>14.4</t>
   </si>
   <si>
@@ -380,10 +377,22 @@
     <t>25일</t>
   </si>
   <si>
+    <t>291.8</t>
+  </si>
+  <si>
+    <t>11454.4</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>114.5</t>
+  </si>
+  <si>
+    <t>26일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>26일</t>
   </si>
   <si>
     <t>27일</t>
@@ -752,10 +761,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s" s="34">
         <v>21</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -763,19 +772,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>23</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>24</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>25</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>26</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -783,19 +792,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>28</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>29</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>30</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>31</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -803,19 +812,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>33</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>34</v>
       </c>
-      <c r="D8" t="s" s="37">
+      <c r="E8" t="s" s="38">
         <v>35</v>
       </c>
-      <c r="E8" t="s" s="38">
+      <c r="F8" t="s" s="39">
         <v>36</v>
-      </c>
-      <c r="F8" t="s" s="39">
-        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -823,19 +832,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>38</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>39</v>
       </c>
-      <c r="D9" t="s" s="32">
+      <c r="E9" t="s" s="33">
         <v>40</v>
       </c>
-      <c r="E9" t="s" s="33">
+      <c r="F9" t="s" s="34">
         <v>41</v>
-      </c>
-      <c r="F9" t="s" s="34">
-        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -843,19 +852,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>43</v>
       </c>
-      <c r="C10" t="s" s="36">
+      <c r="D10" t="s" s="37">
         <v>44</v>
       </c>
-      <c r="D10" t="s" s="37">
+      <c r="E10" t="s" s="38">
         <v>45</v>
       </c>
-      <c r="E10" t="s" s="38">
+      <c r="F10" t="s" s="39">
         <v>46</v>
-      </c>
-      <c r="F10" t="s" s="39">
-        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -863,19 +872,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s" s="31">
         <v>48</v>
       </c>
-      <c r="C11" t="s" s="31">
+      <c r="D11" t="s" s="32">
         <v>49</v>
       </c>
-      <c r="D11" t="s" s="32">
+      <c r="E11" t="s" s="33">
         <v>50</v>
       </c>
-      <c r="E11" t="s" s="33">
+      <c r="F11" t="s" s="34">
         <v>51</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -883,19 +892,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>53</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>54</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s" s="39">
         <v>55</v>
-      </c>
-      <c r="E12" t="s" s="38">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -903,19 +912,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>57</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>58</v>
       </c>
-      <c r="D13" t="s" s="32">
+      <c r="E13" t="s" s="33">
         <v>59</v>
       </c>
-      <c r="E13" t="s" s="33">
+      <c r="F13" t="s" s="34">
         <v>60</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -923,19 +932,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>62</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>63</v>
       </c>
-      <c r="D14" t="s" s="37">
+      <c r="E14" t="s" s="38">
         <v>64</v>
       </c>
-      <c r="E14" t="s" s="38">
+      <c r="F14" t="s" s="39">
         <v>65</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -943,19 +952,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>67</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>68</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>69</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>70</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -963,19 +972,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>72</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>73</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
+        <v>50</v>
+      </c>
+      <c r="F16" t="s" s="39">
         <v>74</v>
-      </c>
-      <c r="E16" t="s" s="38">
-        <v>51</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -983,19 +992,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>76</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>77</v>
       </c>
-      <c r="D17" t="s" s="32">
+      <c r="E17" t="s" s="33">
+        <v>69</v>
+      </c>
+      <c r="F17" t="s" s="34">
         <v>78</v>
-      </c>
-      <c r="E17" t="s" s="33">
-        <v>70</v>
-      </c>
-      <c r="F17" t="s" s="34">
-        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1003,19 +1012,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>80</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>81</v>
       </c>
-      <c r="D18" t="s" s="37">
+      <c r="E18" t="s" s="38">
+        <v>69</v>
+      </c>
+      <c r="F18" t="s" s="39">
         <v>82</v>
-      </c>
-      <c r="E18" t="s" s="38">
-        <v>70</v>
-      </c>
-      <c r="F18" t="s" s="39">
-        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1023,19 +1032,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>84</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>85</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
         <v>86</v>
       </c>
-      <c r="E19" t="s" s="33">
+      <c r="F19" t="s" s="34">
         <v>87</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>88</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1043,19 +1052,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>89</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>90</v>
       </c>
-      <c r="D20" t="s" s="37">
+      <c r="E20" t="s" s="38">
+        <v>64</v>
+      </c>
+      <c r="F20" t="s" s="39">
         <v>91</v>
-      </c>
-      <c r="E20" t="s" s="38">
-        <v>65</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1063,19 +1072,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>93</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>94</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
         <v>95</v>
       </c>
-      <c r="E21" t="s" s="33">
+      <c r="F21" t="s" s="34">
         <v>96</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1083,19 +1092,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>97</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>98</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>99</v>
       </c>
-      <c r="D22" t="s" s="37">
+      <c r="E22" t="s" s="38">
         <v>100</v>
       </c>
-      <c r="E22" t="s" s="38">
+      <c r="F22" t="s" s="39">
         <v>101</v>
-      </c>
-      <c r="F22" t="s" s="39">
-        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1103,19 +1112,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
+        <v>102</v>
+      </c>
+      <c r="C23" t="s" s="31">
         <v>103</v>
       </c>
-      <c r="C23" t="s" s="31">
+      <c r="D23" t="s" s="32">
         <v>104</v>
       </c>
-      <c r="D23" t="s" s="32">
+      <c r="E23" t="s" s="33">
         <v>105</v>
       </c>
-      <c r="E23" t="s" s="33">
+      <c r="F23" t="s" s="34">
         <v>106</v>
-      </c>
-      <c r="F23" t="s" s="34">
-        <v>107</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1123,19 +1132,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
+        <v>107</v>
+      </c>
+      <c r="C24" t="s" s="36">
         <v>108</v>
       </c>
-      <c r="C24" t="s" s="36">
+      <c r="D24" t="s" s="37">
         <v>109</v>
       </c>
-      <c r="D24" t="s" s="37">
+      <c r="E24" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="E24" t="s" s="38">
+      <c r="F24" t="s" s="39">
         <v>111</v>
-      </c>
-      <c r="F24" t="s" s="39">
-        <v>112</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1143,19 +1152,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
+        <v>112</v>
+      </c>
+      <c r="C25" t="s" s="31">
         <v>113</v>
       </c>
-      <c r="C25" t="s" s="31">
+      <c r="D25" t="s" s="32">
         <v>114</v>
       </c>
-      <c r="D25" t="s" s="32">
+      <c r="E25" t="s" s="33">
         <v>115</v>
       </c>
-      <c r="E25" t="s" s="33">
+      <c r="F25" t="s" s="34">
         <v>116</v>
-      </c>
-      <c r="F25" t="s" s="34">
-        <v>117</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1163,19 +1172,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
+        <v>117</v>
+      </c>
+      <c r="C26" t="s" s="36">
+        <v>28</v>
+      </c>
+      <c r="D26" t="s" s="37">
         <v>118</v>
       </c>
-      <c r="C26" t="s" s="36">
-        <v>29</v>
-      </c>
-      <c r="D26" t="s" s="37">
+      <c r="E26" t="s" s="38">
+        <v>30</v>
+      </c>
+      <c r="F26" t="s" s="39">
         <v>119</v>
-      </c>
-      <c r="E26" t="s" s="38">
-        <v>31</v>
-      </c>
-      <c r="F26" t="s" s="39">
-        <v>120</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1183,19 +1192,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s" s="31">
         <v>121</v>
-      </c>
-      <c r="C27" t="s" s="31">
-        <v>122</v>
       </c>
       <c r="D27" t="s" s="32">
         <v>122</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1203,19 +1212,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1223,19 +1232,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1243,19 +1252,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1263,19 +1272,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1283,19 +1292,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="134">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>458.2</t>
+    <t>462.6</t>
   </si>
   <si>
     <t>-</t>
@@ -392,10 +392,19 @@
     <t>26일</t>
   </si>
   <si>
+    <t>574.4</t>
+  </si>
+  <si>
+    <t>12028.8</t>
+  </si>
+  <si>
+    <t>120.3</t>
+  </si>
+  <si>
+    <t>27일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>27일</t>
   </si>
   <si>
     <t>28일</t>
@@ -1218,13 +1227,13 @@
         <v>126</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1232,19 +1241,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1252,19 +1261,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1272,19 +1281,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1292,19 +1301,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="138">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>462.6</t>
+    <t>461.5</t>
   </si>
   <si>
     <t>-</t>
@@ -404,10 +404,22 @@
     <t>27일</t>
   </si>
   <si>
+    <t>433.0</t>
+  </si>
+  <si>
+    <t>12461.8</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>124.6</t>
+  </si>
+  <si>
+    <t>28일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>28일</t>
   </si>
   <si>
     <t>29일</t>
@@ -1247,13 +1259,13 @@
         <v>130</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1261,19 +1273,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1281,19 +1293,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1301,19 +1313,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="142">
   <si>
     <t>No.</t>
   </si>
@@ -35,48 +35,51 @@
     <t>평균</t>
   </si>
   <si>
-    <t>461.5</t>
+    <t>465.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>447.1</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>526.1</t>
+  </si>
+  <si>
+    <t>973.2</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>463.7</t>
+  </si>
+  <si>
+    <t>1436.9</t>
+  </si>
+  <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>447.1</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>526.1</t>
-  </si>
-  <si>
-    <t>973.2</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>463.7</t>
-  </si>
-  <si>
-    <t>1436.9</t>
-  </si>
-  <si>
     <t>14.4</t>
   </si>
   <si>
@@ -419,10 +422,19 @@
     <t>28일</t>
   </si>
   <si>
+    <t>571.3</t>
+  </si>
+  <si>
+    <t>13033.1</t>
+  </si>
+  <si>
+    <t>130.3</t>
+  </si>
+  <si>
+    <t>29일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>29일</t>
   </si>
   <si>
     <t>30일</t>
@@ -782,10 +794,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -793,19 +805,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -813,19 +825,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -833,19 +845,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -853,19 +865,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -873,19 +885,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -893,19 +905,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -913,19 +925,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -933,19 +945,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -953,19 +965,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -973,19 +985,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -993,19 +1005,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1013,19 +1025,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1033,19 +1045,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1053,19 +1065,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1073,19 +1085,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1093,19 +1105,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1113,19 +1125,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1133,19 +1145,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1153,19 +1165,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1173,19 +1185,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1193,19 +1205,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1213,19 +1225,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1233,19 +1245,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1253,19 +1265,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1273,19 +1285,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1293,19 +1305,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1313,19 +1325,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="145">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>465.5</t>
+    <t>468.4</t>
   </si>
   <si>
     <t>-</t>
@@ -422,10 +422,10 @@
     <t>28일</t>
   </si>
   <si>
-    <t>571.3</t>
-  </si>
-  <si>
-    <t>13033.1</t>
+    <t>571.5</t>
+  </si>
+  <si>
+    <t>13033.3</t>
   </si>
   <si>
     <t>130.3</t>
@@ -434,10 +434,19 @@
     <t>29일</t>
   </si>
   <si>
+    <t>551.7</t>
+  </si>
+  <si>
+    <t>13585.0</t>
+  </si>
+  <si>
+    <t>135.8</t>
+  </si>
+  <si>
+    <t>30일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>30일</t>
   </si>
 </sst>
 </file>
@@ -1311,13 +1320,13 @@
         <v>140</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1325,19 +1334,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-06-01.xlsx
+++ b/past_data/site_8023/2026-06-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="147">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>468.4</t>
+    <t>469.4</t>
   </si>
   <si>
     <t>-</t>
@@ -446,7 +446,13 @@
     <t>30일</t>
   </si>
   <si>
-    <t>0.0</t>
+    <t>495.6</t>
+  </si>
+  <si>
+    <t>14080.6</t>
+  </si>
+  <si>
+    <t>140.8</t>
   </si>
 </sst>
 </file>
@@ -1340,13 +1346,13 @@
         <v>144</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>144</v>
+        <v>31</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
